--- a/Vadodara-February-2026.xlsx
+++ b/Vadodara-February-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,31 +94,28 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Vadodara</t>
   </si>
   <si>
     <t>February</t>
   </si>
   <si>
-    <t>GJ01LT9105</t>
-  </si>
-  <si>
-    <t>GJ01MT4472</t>
+    <t>HR55AX6981</t>
+  </si>
+  <si>
+    <t>MH02FG4104</t>
   </si>
   <si>
     <t>MH02FG4096</t>
   </si>
   <si>
-    <t>AMAZE</t>
-  </si>
-  <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>15/05/2025</t>
-  </si>
-  <si>
-    <t>23/03/2021</t>
+    <t>DZIRE</t>
+  </si>
+  <si>
+    <t>CRYSTA</t>
   </si>
 </sst>
 </file>
@@ -480,10 +477,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,120 +559,123 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2026</v>
       </c>
       <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45997</v>
+      </c>
+      <c r="H2">
+        <v>23809</v>
+      </c>
+      <c r="I2">
+        <v>28402</v>
+      </c>
+      <c r="J2">
+        <v>4593</v>
+      </c>
+      <c r="K2">
+        <v>4597</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4597</v>
+      </c>
+      <c r="O2">
+        <v>-4</v>
+      </c>
+      <c r="P2">
+        <v>111610</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>111610</v>
+      </c>
+      <c r="T2">
+        <v>26588</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>20145</v>
+      </c>
+      <c r="W2">
+        <v>18470</v>
+      </c>
+      <c r="X2">
+        <v>65203</v>
+      </c>
+      <c r="Y2">
+        <v>46407</v>
+      </c>
+      <c r="Z2">
+        <v>41.58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
+      <c r="A3">
+        <v>271</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
         <v>28</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2">
-        <v>30009</v>
-      </c>
-      <c r="I2">
-        <v>33971</v>
-      </c>
-      <c r="J2">
-        <v>3962</v>
-      </c>
-      <c r="K2">
-        <v>3918</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>3918</v>
-      </c>
-      <c r="O2">
-        <v>44</v>
-      </c>
-      <c r="P2">
-        <v>125559</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>125559</v>
-      </c>
-      <c r="T2">
-        <v>31542</v>
-      </c>
-      <c r="U2">
-        <v>4664</v>
-      </c>
-      <c r="V2">
-        <v>15616</v>
-      </c>
-      <c r="W2">
-        <v>19754</v>
-      </c>
-      <c r="X2">
-        <v>71576</v>
-      </c>
-      <c r="Y2">
-        <v>53983</v>
-      </c>
-      <c r="Z2">
-        <v>42.99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26">
-      <c r="A3">
-        <v>269</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
       </c>
       <c r="D3">
         <v>2026</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="G3" s="2">
+        <v>44471</v>
       </c>
       <c r="H3">
-        <v>105831</v>
+        <v>73824</v>
       </c>
       <c r="I3">
-        <v>109055</v>
+        <v>75708</v>
       </c>
       <c r="J3">
-        <v>3224</v>
+        <v>1884</v>
       </c>
       <c r="K3">
-        <v>3197</v>
+        <v>1770</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -684,63 +684,63 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>3197</v>
+        <v>1770</v>
       </c>
       <c r="O3">
+        <v>114</v>
+      </c>
+      <c r="P3">
+        <v>56945</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>56945</v>
+      </c>
+      <c r="T3">
+        <v>10766</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>10278</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>21044</v>
+      </c>
+      <c r="Y3">
+        <v>35901</v>
+      </c>
+      <c r="Z3">
+        <v>63.04</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
+      <c r="A4">
+        <v>272</v>
+      </c>
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="P3">
-        <v>165421</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>165421</v>
-      </c>
-      <c r="T3">
-        <v>27180</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>20574</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>47754</v>
-      </c>
-      <c r="Y3">
-        <v>117667</v>
-      </c>
-      <c r="Z3">
-        <v>71.13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26">
-      <c r="A4">
-        <v>270</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2026</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2">
         <v>44441</v>
